--- a/从零开始学Slots/从零开始学Slots-16-数值篇-WaySlots(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-16-数值篇-WaySlots(1).xlsx
@@ -7855,6 +7855,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N150" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9036,5 +9039,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:R87" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-16-数值篇-WaySlots(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-16-数值篇-WaySlots(1).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="210">
   <si>
     <r>
       <rPr>
@@ -6659,11 +6659,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6847,7 +6848,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6986,6 +6987,22 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7747,8 +7764,8 @@
       <c r="A108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="s">
-        <v>82</v>
+      <c r="A109" s="35">
+        <v>1</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7921,8 +7938,8 @@
       <c r="B5" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>106</v>
+      <c r="C5" s="36">
+        <v>3</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -8507,8 +8524,8 @@
         <f aca="false">E37*F37</f>
         <v>0.31146240234375</v>
       </c>
-      <c r="H37" s="19" t="s">
-        <v>155</v>
+      <c r="H37" s="37">
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8536,8 +8553,8 @@
         <f aca="false">E38*F38</f>
         <v>0.233596801757813</v>
       </c>
-      <c r="H38" s="19" t="s">
-        <v>157</v>
+      <c r="H38" s="37">
+        <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8565,8 +8582,8 @@
         <f aca="false">E39*F39</f>
         <v>12.2638320922852</v>
       </c>
-      <c r="H39" s="19" t="s">
-        <v>159</v>
+      <c r="H39" s="37">
+        <v>5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8594,8 +8611,8 @@
         <f aca="false">E40*F40</f>
         <v>0.3955078125</v>
       </c>
-      <c r="H40" s="19" t="s">
-        <v>161</v>
+      <c r="H40" s="37">
+        <v>3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8623,8 +8640,8 @@
         <f aca="false">E41*F41</f>
         <v>1.3348388671875</v>
       </c>
-      <c r="H41" s="19" t="s">
-        <v>163</v>
+      <c r="H41" s="37">
+        <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8652,8 +8669,8 @@
         <f aca="false">E42*F42</f>
         <v>16.6854858398438</v>
       </c>
-      <c r="H42" s="19" t="s">
-        <v>165</v>
+      <c r="H42" s="37">
+        <v>5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8681,8 +8698,8 @@
         <f aca="false">E43*F43</f>
         <v>0.0889892578125</v>
       </c>
-      <c r="H43" s="19" t="s">
-        <v>161</v>
+      <c r="H43" s="37">
+        <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8710,8 +8727,8 @@
         <f aca="false">E44*F44</f>
         <v>0.700790405273438</v>
       </c>
-      <c r="H44" s="19" t="s">
-        <v>163</v>
+      <c r="H44" s="37">
+        <v>4</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8739,8 +8756,8 @@
         <f aca="false">E45*F45</f>
         <v>8.75988006591797</v>
       </c>
-      <c r="H45" s="19" t="s">
-        <v>165</v>
+      <c r="H45" s="37">
+        <v>5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8934,8 +8951,8 @@
         <f aca="false">IF(B9=B8^B6,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C61" s="19" t="s">
-        <v>200</v>
+      <c r="C61" s="38">
+        <v>1048576</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8946,8 +8963,8 @@
         <f aca="false">IF(SUMPRODUCT(--(ABS(E37:E45-C37:C45/D37:D45)&lt;0.000001))=9,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C62" s="19" t="s">
-        <v>202</v>
+      <c r="C62" s="37">
+        <v>9</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/从零开始学Slots/从零开始学Slots-16-数值篇-WaySlots(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-16-数值篇-WaySlots(1).xlsx
@@ -6659,12 +6659,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6848,7 +6849,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7002,6 +7003,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8513,7 +8518,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="39" t="n">
         <f aca="false">C37/D37</f>
         <v>0.31146240234375</v>
       </c>
@@ -8542,7 +8547,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E38" s="24" t="n">
+      <c r="E38" s="39" t="n">
         <f aca="false">C38/D38</f>
         <v>0.116798400878906</v>
       </c>
@@ -8571,7 +8576,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E39" s="24" t="n">
+      <c r="E39" s="39" t="n">
         <f aca="false">C39/D39</f>
         <v>2.45276641845703</v>
       </c>
@@ -8600,7 +8605,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E40" s="24" t="n">
+      <c r="E40" s="39" t="n">
         <f aca="false">C40/D40</f>
         <v>0.19775390625</v>
       </c>
@@ -8629,7 +8634,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E41" s="24" t="n">
+      <c r="E41" s="39" t="n">
         <f aca="false">C41/D41</f>
         <v>0.333709716796875</v>
       </c>
@@ -8658,7 +8663,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="39" t="n">
         <f aca="false">C42/D42</f>
         <v>1.66854858398438</v>
       </c>
@@ -8687,7 +8692,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="39" t="n">
         <f aca="false">C43/D43</f>
         <v>0.0296630859375</v>
       </c>
@@ -8716,7 +8721,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="39" t="n">
         <f aca="false">C44/D44</f>
         <v>0.116798400878906</v>
       </c>
@@ -8745,7 +8750,7 @@
         <f aca="false">$B$9</f>
         <v>1048576</v>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="39" t="n">
         <f aca="false">C45/D45</f>
         <v>0.583992004394531</v>
       </c>
